--- a/Result/profitability/5522.xlsx
+++ b/Result/profitability/5522.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5875</v>
+        <v>1.425</v>
       </c>
       <c r="N2" t="n">
-        <v>32.1625</v>
+        <v>32.6625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5725</v>
+        <v>1.48875</v>
       </c>
       <c r="N3" t="n">
-        <v>32.91875</v>
+        <v>32.92749999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.24</v>
       </c>
       <c r="M4" t="n">
-        <v>1.74</v>
+        <v>1.79875</v>
       </c>
       <c r="N4" t="n">
-        <v>33.35875</v>
+        <v>34.56</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.93875</v>
+        <v>2.01</v>
       </c>
       <c r="N5" t="n">
-        <v>35.2875</v>
+        <v>36.35375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>2.15625</v>
+        <v>1.895</v>
       </c>
       <c r="N6" t="n">
-        <v>37.34375</v>
+        <v>36.93625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9425</v>
+        <v>1.25625</v>
       </c>
       <c r="N7" t="n">
-        <v>37.75375</v>
+        <v>37.61375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.69</v>
       </c>
       <c r="M8" t="n">
-        <v>1.56375</v>
+        <v>1.3725</v>
       </c>
       <c r="N8" t="n">
-        <v>38.76625</v>
+        <v>38.25375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>2.19</v>
       </c>
       <c r="N10" t="n">
-        <v>40.385</v>
+        <v>40.38500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>2.35</v>
       </c>
       <c r="N12" t="n">
-        <v>41.74124999999999</v>
+        <v>41.74125</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5522</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2868</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1929</v>
+      </c>
+      <c r="E75" t="n">
+        <v>939</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>510</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="J75" t="n">
+        <v>484</v>
+      </c>
+      <c r="K75" t="n">
+        <v>179</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.03375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8693181818181819</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.100000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1112618724559024</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.676470588235294</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.530000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3521882741535922</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
